--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="360">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-18T07:48:41+00:00</t>
+    <t>2023-08-24T08:11:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -147,6 +147,10 @@
   </si>
   <si>
     <t>Demographics and other administrative information about an individual or animal receiving care or other health-related services.</t>
+  </si>
+  <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Patient.id</t>
@@ -1452,7 +1456,7 @@
         <v>2</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="23">
@@ -1460,7 +1464,7 @@
         <v>4</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="24">
@@ -1476,7 +1480,7 @@
         <v>8</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="26">
@@ -1528,7 +1532,7 @@
         <v>21</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33">
@@ -1556,7 +1560,7 @@
         <v>27</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="37">
@@ -1564,7 +1568,7 @@
         <v>29</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38">
@@ -1572,7 +1576,7 @@
         <v>31</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="39">
@@ -1593,10 +1597,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -1745,7 +1749,7 @@
         <v>40</v>
       </c>
       <c r="AK1" t="s" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
@@ -1753,10 +1757,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" t="s" s="2">
@@ -1767,7 +1771,7 @@
         <v>38</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I2" t="s" s="2">
         <v>40</v>
@@ -1776,19 +1780,19 @@
         <v>40</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O2" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" t="s" s="2">
@@ -1838,13 +1842,13 @@
         <v>40</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AH2" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ2" t="s" s="2">
         <v>40</v>
@@ -1858,10 +1862,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" t="s" s="2">
@@ -1872,7 +1876,7 @@
         <v>38</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>40</v>
@@ -1881,16 +1885,16 @@
         <v>40</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
@@ -1941,19 +1945,19 @@
         <v>40</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
@@ -1961,10 +1965,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" t="s" s="2">
@@ -1975,28 +1979,28 @@
         <v>38</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N4" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O4" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" t="s" s="2">
@@ -2046,19 +2050,19 @@
         <v>40</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AH4" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -2066,10 +2070,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" t="s" s="2">
@@ -2080,7 +2084,7 @@
         <v>38</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>40</v>
@@ -2092,16 +2096,16 @@
         <v>40</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O5" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" t="s" s="2">
@@ -2127,13 +2131,13 @@
         <v>40</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AB5" t="s" s="2">
         <v>40</v>
@@ -2151,19 +2155,19 @@
         <v>40</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
@@ -2171,21 +2175,21 @@
         <v>3</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>40</v>
@@ -2197,16 +2201,16 @@
         <v>40</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" t="s" s="2">
@@ -2256,19 +2260,19 @@
         <v>40</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH6" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -2276,14 +2280,14 @@
         <v>3</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" t="s" s="2">
@@ -2302,16 +2306,16 @@
         <v>40</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" t="s" s="2">
@@ -2361,7 +2365,7 @@
         <v>40</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH7" t="s" s="2">
         <v>38</v>
@@ -2381,14 +2385,14 @@
         <v>3</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" t="s" s="2">
@@ -2407,16 +2411,16 @@
         <v>40</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" t="s" s="2">
@@ -2454,19 +2458,19 @@
         <v>40</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE8" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>38</v>
@@ -2475,10 +2479,10 @@
         <v>39</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9">
@@ -2486,13 +2490,13 @@
         <v>3</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s" s="2">
         <v>40</v>
@@ -2502,10 +2506,10 @@
         <v>38</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J9" t="s" s="2">
         <v>40</v>
@@ -2514,13 +2518,13 @@
         <v>40</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
@@ -2571,7 +2575,7 @@
         <v>40</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AH9" t="s" s="2">
         <v>38</v>
@@ -2580,10 +2584,10 @@
         <v>39</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -2591,14 +2595,14 @@
         <v>3</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" t="s" s="2">
@@ -2611,25 +2615,25 @@
         <v>40</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>40</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q10" t="s" s="2">
         <v>40</v>
@@ -2666,19 +2670,19 @@
         <v>40</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE10" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH10" t="s" s="2">
         <v>38</v>
@@ -2687,10 +2691,10 @@
         <v>39</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
@@ -2698,10 +2702,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" t="s" s="2">
@@ -2709,7 +2713,7 @@
       </c>
       <c r="F11" s="2"/>
       <c r="G11" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>39</v>
@@ -2721,20 +2725,20 @@
         <v>40</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q11" t="s" s="2">
         <v>40</v>
@@ -2771,19 +2775,19 @@
         <v>40</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AE11" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AH11" t="s" s="2">
         <v>38</v>
@@ -2792,10 +2796,10 @@
         <v>39</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
@@ -2803,45 +2807,45 @@
         <v>3</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E12" t="s" s="2">
         <v>40</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>40</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q12" t="s" s="2">
         <v>40</v>
@@ -2890,7 +2894,7 @@
         <v>40</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AH12" t="s" s="2">
         <v>38</v>
@@ -2899,10 +2903,10 @@
         <v>39</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -2910,10 +2914,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
@@ -2924,7 +2928,7 @@
         <v>38</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>40</v>
@@ -2936,13 +2940,13 @@
         <v>40</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -2993,13 +2997,13 @@
         <v>40</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>40</v>
@@ -3013,14 +3017,14 @@
         <v>3</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" t="s" s="2">
@@ -3039,16 +3043,16 @@
         <v>40</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P14" s="2"/>
       <c r="Q14" t="s" s="2">
@@ -3086,19 +3090,19 @@
         <v>40</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE14" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>38</v>
@@ -3107,10 +3111,10 @@
         <v>39</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -3118,10 +3122,10 @@
         <v>3</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
@@ -3132,31 +3136,31 @@
         <v>38</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q15" t="s" s="2">
         <v>40</v>
@@ -3181,13 +3185,13 @@
         <v>40</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AB15" t="s" s="2">
         <v>40</v>
@@ -3205,19 +3209,19 @@
         <v>40</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">
@@ -3225,10 +3229,10 @@
         <v>3</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
@@ -3239,7 +3243,7 @@
         <v>38</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>40</v>
@@ -3248,22 +3252,22 @@
         <v>40</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P16" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q16" t="s" s="2">
         <v>40</v>
@@ -3288,13 +3292,13 @@
         <v>40</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AB16" t="s" s="2">
         <v>40</v>
@@ -3312,19 +3316,19 @@
         <v>40</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
@@ -3332,10 +3336,10 @@
         <v>3</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
@@ -3343,10 +3347,10 @@
       </c>
       <c r="F17" s="2"/>
       <c r="G17" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>40</v>
@@ -3355,22 +3359,22 @@
         <v>40</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P17" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q17" t="s" s="2">
         <v>40</v>
@@ -3380,10 +3384,10 @@
         <v>40</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V17" t="s" s="2">
         <v>40</v>
@@ -3419,19 +3423,19 @@
         <v>40</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
@@ -3439,10 +3443,10 @@
         <v>3</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
@@ -3453,7 +3457,7 @@
         <v>38</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>40</v>
@@ -3462,19 +3466,19 @@
         <v>40</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" t="s" s="2">
@@ -3488,7 +3492,7 @@
         <v>40</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="V18" t="s" s="2">
         <v>40</v>
@@ -3524,19 +3528,19 @@
         <v>40</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -3544,10 +3548,10 @@
         <v>3</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
@@ -3558,7 +3562,7 @@
         <v>38</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>40</v>
@@ -3567,19 +3571,19 @@
         <v>40</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P19" s="2"/>
       <c r="Q19" t="s" s="2">
@@ -3629,19 +3633,19 @@
         <v>40</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20">
@@ -3649,10 +3653,10 @@
         <v>3</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
@@ -3663,7 +3667,7 @@
         <v>38</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>40</v>
@@ -3672,19 +3676,19 @@
         <v>40</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P20" s="2"/>
       <c r="Q20" t="s" s="2">
@@ -3734,19 +3738,19 @@
         <v>40</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21">
@@ -3754,10 +3758,10 @@
         <v>3</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -3768,94 +3772,94 @@
         <v>38</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="P21" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Q21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="R21" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AG21" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M21" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="P21" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Q21" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="R21" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>181</v>
-      </c>
       <c r="AH21" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22">
@@ -3863,10 +3867,10 @@
         <v>3</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -3886,22 +3890,22 @@
         <v>40</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P22" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q22" t="s" s="2">
         <v>40</v>
@@ -3950,7 +3954,7 @@
         <v>40</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>38</v>
@@ -3959,10 +3963,10 @@
         <v>39</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
@@ -3970,10 +3974,10 @@
         <v>3</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
@@ -3993,22 +3997,22 @@
         <v>40</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P23" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q23" t="s" s="2">
         <v>40</v>
@@ -4057,7 +4061,7 @@
         <v>40</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>38</v>
@@ -4066,10 +4070,10 @@
         <v>39</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24">
@@ -4077,10 +4081,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
@@ -4091,7 +4095,7 @@
         <v>38</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>40</v>
@@ -4100,22 +4104,22 @@
         <v>40</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P24" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q24" t="s" s="2">
         <v>40</v>
@@ -4140,11 +4144,11 @@
         <v>40</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Z24" s="2"/>
       <c r="AA24" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AB24" t="s" s="2">
         <v>40</v>
@@ -4162,19 +4166,19 @@
         <v>40</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25">
@@ -4182,10 +4186,10 @@
         <v>3</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
@@ -4196,7 +4200,7 @@
         <v>38</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>40</v>
@@ -4205,22 +4209,22 @@
         <v>40</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P25" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q25" t="s" s="2">
         <v>40</v>
@@ -4269,19 +4273,19 @@
         <v>40</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26">
@@ -4289,10 +4293,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -4303,31 +4307,31 @@
         <v>38</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P26" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q26" t="s" s="2">
         <v>40</v>
@@ -4376,19 +4380,19 @@
         <v>40</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27">
@@ -4396,10 +4400,10 @@
         <v>3</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
@@ -4419,22 +4423,22 @@
         <v>40</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q27" t="s" s="2">
         <v>40</v>
@@ -4483,7 +4487,7 @@
         <v>40</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>38</v>
@@ -4492,10 +4496,10 @@
         <v>39</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28">
@@ -4503,10 +4507,10 @@
         <v>3</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -4517,7 +4521,7 @@
         <v>38</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>40</v>
@@ -4529,19 +4533,19 @@
         <v>40</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P28" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q28" t="s" s="2">
         <v>40</v>
@@ -4566,13 +4570,13 @@
         <v>40</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AB28" t="s" s="2">
         <v>40</v>
@@ -4590,19 +4594,19 @@
         <v>40</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29">
@@ -4610,10 +4614,10 @@
         <v>3</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -4624,7 +4628,7 @@
         <v>38</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>40</v>
@@ -4636,19 +4640,19 @@
         <v>40</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P29" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q29" t="s" s="2">
         <v>40</v>
@@ -4697,19 +4701,19 @@
         <v>40</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30">
@@ -4717,10 +4721,10 @@
         <v>3</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -4743,19 +4747,19 @@
         <v>40</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P30" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q30" t="s" s="2">
         <v>40</v>
@@ -4804,7 +4808,7 @@
         <v>40</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>38</v>
@@ -4813,10 +4817,10 @@
         <v>39</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="31">
@@ -4824,10 +4828,10 @@
         <v>3</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -4850,19 +4854,19 @@
         <v>40</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P31" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q31" t="s" s="2">
         <v>40</v>
@@ -4911,7 +4915,7 @@
         <v>40</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>38</v>
@@ -4920,10 +4924,10 @@
         <v>39</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="32">
@@ -4931,10 +4935,10 @@
         <v>3</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -4945,7 +4949,7 @@
         <v>38</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>40</v>
@@ -4957,13 +4961,13 @@
         <v>40</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -5014,13 +5018,13 @@
         <v>40</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>40</v>
@@ -5034,14 +5038,14 @@
         <v>3</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" t="s" s="2">
@@ -5060,16 +5064,16 @@
         <v>40</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P33" s="2"/>
       <c r="Q33" t="s" s="2">
@@ -5107,19 +5111,19 @@
         <v>40</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE33" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>38</v>
@@ -5128,10 +5132,10 @@
         <v>39</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34">
@@ -5139,14 +5143,14 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" t="s" s="2">
@@ -5159,25 +5163,25 @@
         <v>40</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P34" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q34" t="s" s="2">
         <v>40</v>
@@ -5226,7 +5230,7 @@
         <v>40</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>38</v>
@@ -5235,10 +5239,10 @@
         <v>39</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35">
@@ -5246,10 +5250,10 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -5272,19 +5276,19 @@
         <v>40</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P35" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q35" t="s" s="2">
         <v>40</v>
@@ -5309,13 +5313,13 @@
         <v>40</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AB35" t="s" s="2">
         <v>40</v>
@@ -5333,7 +5337,7 @@
         <v>40</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>38</v>
@@ -5342,10 +5346,10 @@
         <v>39</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36">
@@ -5353,10 +5357,10 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -5367,7 +5371,7 @@
         <v>38</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>40</v>
@@ -5379,19 +5383,19 @@
         <v>40</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P36" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q36" t="s" s="2">
         <v>40</v>
@@ -5440,19 +5444,19 @@
         <v>40</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37">
@@ -5460,10 +5464,10 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -5486,19 +5490,19 @@
         <v>40</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P37" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q37" t="s" s="2">
         <v>40</v>
@@ -5547,7 +5551,7 @@
         <v>40</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>38</v>
@@ -5556,10 +5560,10 @@
         <v>39</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="38">
@@ -5567,10 +5571,10 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -5581,7 +5585,7 @@
         <v>38</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>40</v>
@@ -5593,19 +5597,19 @@
         <v>40</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P38" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q38" t="s" s="2">
         <v>40</v>
@@ -5654,19 +5658,19 @@
         <v>40</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39">
@@ -5674,10 +5678,10 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -5688,7 +5692,7 @@
         <v>38</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>40</v>
@@ -5700,19 +5704,19 @@
         <v>40</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P39" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q39" t="s" s="2">
         <v>40</v>
@@ -5737,13 +5741,13 @@
         <v>40</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AB39" t="s" s="2">
         <v>40</v>
@@ -5761,19 +5765,19 @@
         <v>40</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40">
@@ -5781,10 +5785,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -5795,7 +5799,7 @@
         <v>38</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>40</v>
@@ -5807,19 +5811,19 @@
         <v>40</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P40" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q40" t="s" s="2">
         <v>40</v>
@@ -5868,19 +5872,19 @@
         <v>40</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41">
@@ -5888,10 +5892,10 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -5902,7 +5906,7 @@
         <v>38</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>40</v>
@@ -5914,16 +5918,16 @@
         <v>40</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P41" s="2"/>
       <c r="Q41" t="s" s="2">
@@ -5973,19 +5977,19 @@
         <v>40</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="42">
@@ -5993,10 +5997,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6019,19 +6023,19 @@
         <v>40</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P42" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q42" t="s" s="2">
         <v>40</v>
@@ -6080,7 +6084,7 @@
         <v>40</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>38</v>
@@ -6089,10 +6093,10 @@
         <v>39</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43">
@@ -6100,10 +6104,10 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -6114,7 +6118,7 @@
         <v>38</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>40</v>
@@ -6126,13 +6130,13 @@
         <v>40</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" s="2"/>
@@ -6183,13 +6187,13 @@
         <v>40</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>40</v>
@@ -6203,14 +6207,14 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" t="s" s="2">
@@ -6229,16 +6233,16 @@
         <v>40</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P44" s="2"/>
       <c r="Q44" t="s" s="2">
@@ -6276,19 +6280,19 @@
         <v>40</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD44" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE44" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>38</v>
@@ -6297,10 +6301,10 @@
         <v>39</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45">
@@ -6308,14 +6312,14 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" t="s" s="2">
@@ -6328,25 +6332,25 @@
         <v>40</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P45" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q45" t="s" s="2">
         <v>40</v>
@@ -6395,7 +6399,7 @@
         <v>40</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>38</v>
@@ -6404,10 +6408,10 @@
         <v>39</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46">
@@ -6415,10 +6419,10 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -6426,10 +6430,10 @@
       </c>
       <c r="F46" s="2"/>
       <c r="G46" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>40</v>
@@ -6441,19 +6445,19 @@
         <v>40</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P46" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q46" t="s" s="2">
         <v>40</v>
@@ -6478,13 +6482,13 @@
         <v>40</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AB46" t="s" s="2">
         <v>40</v>
@@ -6502,19 +6506,19 @@
         <v>40</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47">
@@ -6522,10 +6526,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -6536,7 +6540,7 @@
         <v>38</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>40</v>
@@ -6548,19 +6552,19 @@
         <v>40</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P47" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q47" t="s" s="2">
         <v>40</v>
@@ -6609,19 +6613,19 @@
         <v>40</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48">
@@ -6629,14 +6633,14 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" t="s" s="2">
@@ -6655,16 +6659,16 @@
         <v>40</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P48" s="2"/>
       <c r="Q48" t="s" s="2">
@@ -6714,7 +6718,7 @@
         <v>40</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>38</v>
@@ -6723,10 +6727,10 @@
         <v>39</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="49">
@@ -6734,10 +6738,10 @@
         <v>3</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -6748,7 +6752,7 @@
         <v>38</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>40</v>
@@ -6757,22 +6761,22 @@
         <v>40</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q49" t="s" s="2">
         <v>40</v>
@@ -6821,19 +6825,19 @@
         <v>40</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="50">
@@ -6841,10 +6845,10 @@
         <v>3</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -6861,25 +6865,25 @@
         <v>40</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P50" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q50" t="s" s="2">
         <v>40</v>
@@ -6928,7 +6932,7 @@
         <v>40</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>38</v>
@@ -6937,10 +6941,10 @@
         <v>39</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51">
@@ -6948,10 +6952,10 @@
         <v>3</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -6962,7 +6966,7 @@
         <v>38</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>40</v>
@@ -6974,13 +6978,13 @@
         <v>40</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
@@ -7031,13 +7035,13 @@
         <v>40</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>40</v>
@@ -7051,14 +7055,14 @@
         <v>3</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" t="s" s="2">
@@ -7077,16 +7081,16 @@
         <v>40</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P52" s="2"/>
       <c r="Q52" t="s" s="2">
@@ -7124,19 +7128,19 @@
         <v>40</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD52" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE52" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>38</v>
@@ -7145,10 +7149,10 @@
         <v>39</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53">
@@ -7156,14 +7160,14 @@
         <v>3</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" t="s" s="2">
@@ -7176,25 +7180,25 @@
         <v>40</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P53" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q53" t="s" s="2">
         <v>40</v>
@@ -7243,7 +7247,7 @@
         <v>40</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>38</v>
@@ -7252,10 +7256,10 @@
         <v>39</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54">
@@ -7263,10 +7267,10 @@
         <v>3</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -7274,10 +7278,10 @@
       </c>
       <c r="F54" s="2"/>
       <c r="G54" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>40</v>
@@ -7286,19 +7290,19 @@
         <v>40</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P54" s="2"/>
       <c r="Q54" t="s" s="2">
@@ -7348,19 +7352,19 @@
         <v>40</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="55">
@@ -7368,10 +7372,10 @@
         <v>3</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -7379,10 +7383,10 @@
       </c>
       <c r="F55" s="2"/>
       <c r="G55" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>40</v>
@@ -7391,19 +7395,19 @@
         <v>40</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P55" s="2"/>
       <c r="Q55" t="s" s="2">
@@ -7429,13 +7433,13 @@
         <v>40</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AB55" t="s" s="2">
         <v>40</v>
@@ -7453,30 +7457,30 @@
         <v>40</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -7502,10 +7506,10 @@
         <v>41</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" s="2"/>
@@ -7556,7 +7560,7 @@
         <v>40</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>38</v>
@@ -7565,21 +7569,21 @@
         <v>39</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>40</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -7590,7 +7594,7 @@
         <v>38</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>40</v>
@@ -7602,13 +7606,13 @@
         <v>40</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
@@ -7659,13 +7663,13 @@
         <v>40</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>40</v>
@@ -7676,13 +7680,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -7705,13 +7709,13 @@
         <v>40</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
@@ -7750,19 +7754,19 @@
         <v>40</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD58" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AE58" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>38</v>
@@ -7771,21 +7775,21 @@
         <v>39</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -7793,10 +7797,10 @@
       </c>
       <c r="F59" s="2"/>
       <c r="G59" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>40</v>
@@ -7808,16 +7812,16 @@
         <v>40</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P59" s="2"/>
       <c r="Q59" t="s" s="2">
@@ -7825,7 +7829,7 @@
       </c>
       <c r="R59" s="2"/>
       <c r="S59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>40</v>
@@ -7867,13 +7871,13 @@
         <v>40</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>40</v>
@@ -7884,13 +7888,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -7901,7 +7905,7 @@
         <v>38</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>40</v>
@@ -7913,13 +7917,13 @@
         <v>40</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
@@ -7946,11 +7950,11 @@
         <v>40</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Z60" s="2"/>
       <c r="AA60" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AB60" t="s" s="2">
         <v>40</v>
@@ -7968,19 +7972,19 @@
         <v>40</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-24T08:11:25+00:00</t>
+    <t>2023-09-06T14:38:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-13T15:12:43+00:00</t>
+    <t>2023-12-13T15:24:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-13T15:24:56+00:00</t>
+    <t>2023-12-13T15:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-13T15:28:34+00:00</t>
+    <t>2024-02-12T12:57:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T12:57:06+00:00</t>
+    <t>2024-02-12T12:59:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T12:59:31+00:00</t>
+    <t>2024-02-12T14:31:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:31:30+00:00</t>
+    <t>2024-02-12T16:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T16:33:03+00:00</t>
+    <t>2024-02-12T16:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T16:38:55+00:00</t>
+    <t>2024-02-12T16:39:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T16:39:27+00:00</t>
+    <t>2024-02-12T16:43:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot</t>
+    <t>1.0.1-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T16:43:27+00:00</t>
+    <t>2024-02-13T13:14:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T13:14:14+00:00</t>
+    <t>2024-02-14T14:30:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-14T14:30:45+00:00</t>
+    <t>2024-02-15T09:58:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T09:58:35+00:00</t>
+    <t>2024-02-15T09:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T09:59:20+00:00</t>
+    <t>2024-02-15T10:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T10:29:18+00:00</t>
+    <t>2024-02-15T10:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T10:48:09+00:00</t>
+    <t>2024-02-15T10:48:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T10:48:23+00:00</t>
+    <t>2024-02-15T10:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T10:53:05+00:00</t>
+    <t>2024-02-15T10:58:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T10:58:34+00:00</t>
+    <t>2024-02-15T11:00:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T11:00:02+00:00</t>
+    <t>2024-02-15T11:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T11:15:07+00:00</t>
+    <t>2024-02-15T11:15:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T11:15:53+00:00</t>
+    <t>2024-02-15T12:51:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T12:51:15+00:00</t>
+    <t>2024-02-15T15:41:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T15:41:42+00:00</t>
+    <t>2024-02-16T12:54:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T12:54:40+00:00</t>
+    <t>2024-02-16T16:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/all-profiles.xlsx
+++ b/ig/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T16:35:16+00:00</t>
+    <t>2024-02-19T08:17:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
